--- a/docs/demo/diem_INT301_hop_le.xlsx
+++ b/docs/demo/diem_INT301_hop_le.xlsx
@@ -63,7 +63,7 @@
     <x:t>Ngày xuất:</x:t>
   </x:si>
   <x:si>
-    <x:t>28/10/2026 21:11</x:t>
+    <x:t>29/10/2026 18:51</x:t>
   </x:si>
   <x:si>
     <x:t>Ghi chú:</x:t>
